--- a/docs/feature-tracking/products-feature-matrix.xlsx
+++ b/docs/feature-tracking/products-feature-matrix.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Activity log (audit trail)</t>
+          <t>Cloud backup (automatic, multi-provider, retention)</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Record user actions.</t>
+          <t>Upload a portable backup to Google Drive/Dropbox/4shared/S3/local mirror on a schedule, with retention pruning.</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>T: activity.php; N: 'activity log audit screen' bespoke (NOT-IMPLEMENTED §2).</t>
+          <t>L: backup:cloud + 5-min dispatcher; P: scripts/backup-cloud.php + cron; T: inc/cloud-backup.php + WP-cron; N: lib/cloud-backup.ts + dispatch. See docs/design/CLOUD-BACKUP.md.</t>
         </is>
       </c>
     </row>
@@ -7957,17 +7957,17 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Visitor logs</t>
+          <t>Configurable document designs &amp; watermarks</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Track visitor paths/locations.</t>
+          <t>Per-type themes (colours/fonts/borders/templates) + optional watermark for certificates, testimonials, marksheets, admit cards, ID cards.</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>T: visitor-logs.php; N: engine CRUD.</t>
+          <t>L: DocumentDesignService + document-designs admin; P: same service (byte-identical views); T: inc/document-designs.php; N: lib/document-designs.ts + dashboard page. See docs/design/DOCUMENT-DESIGNS.md.</t>
         </is>
       </c>
     </row>
@@ -8027,12 +8027,12 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Cache / tools admin</t>
+          <t>Activity log (audit trail)</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Clear caches + maintenance tools.</t>
+          <t>Record user actions.</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>T: cache.php / tools.php (theme tokens, parity §1); N: settings/tools surface.</t>
+          <t>T: activity.php; N: 'activity log audit screen' bespoke (NOT-IMPLEMENTED §2).</t>
         </is>
       </c>
     </row>
@@ -8092,12 +8092,12 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Mail settings + templates</t>
+          <t>Visitor logs</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>SMTP config + email templates.</t>
+          <t>Track visitor paths/locations.</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -8105,9 +8105,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -8115,24 +8115,24 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H117" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I117" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="J117" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="K117" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>N: mail_enabled + SMTP settings form, no queue/mailer (NOT-IMPLEMENTED §5).</t>
+          <t>T: visitor-logs.php; N: engine CRUD.</t>
         </is>
       </c>
     </row>
@@ -8157,55 +8157,185 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
+          <t>Cache / tools admin</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Clear caches + maintenance tools.</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J118" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L118" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M118" s="4" t="inlineStr">
+        <is>
+          <t>T: cache.php / tools.php (theme tokens, parity §1); N: settings/tools surface.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Mail settings + templates</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>SMTP config + email templates.</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J119" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="K119" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="L119" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M119" s="4" t="inlineStr">
+        <is>
+          <t>N: mail_enabled + SMTP settings form, no queue/mailer (NOT-IMPLEMENTED §5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
           <t>Push notifications (FCM)</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D120" s="4" t="inlineStr">
         <is>
           <t>Firebase push delivery.</t>
         </is>
       </c>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="inlineStr">
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="inlineStr">
         <is>
           <t>Not tested</t>
         </is>
       </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H118" s="8" t="inlineStr">
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="inlineStr">
         <is>
           <t>Not tested</t>
         </is>
       </c>
-      <c r="I118" s="7" t="inlineStr">
+      <c r="I120" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J118" s="8" t="inlineStr">
+      <c r="J120" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K118" s="7" t="inlineStr">
+      <c r="K120" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L118" s="8" t="inlineStr">
+      <c r="L120" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M118" s="4" t="inlineStr">
+      <c r="M120" s="4" t="inlineStr">
         <is>
           <t>L/P: PUSH_DRIVER firebase in .env; T/N: not present.</t>
         </is>
@@ -8303,28 +8433,28 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>100</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>82.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>75.2</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -8352,10 +8482,10 @@
         <v>3.4</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="7">
@@ -8380,13 +8510,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="8">
@@ -8396,16 +8526,16 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>100</v>
@@ -8461,16 +8591,16 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -9031,7 +9161,7 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>

--- a/docs/feature-tracking/products-feature-matrix.xlsx
+++ b/docs/feature-tracking/products-feature-matrix.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4261,12 +4261,12 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Offline / bank-transfer payments</t>
+          <t>Payment gateways — test/sandbox (zero-cost diagnostics)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Manual offline payment approvals.</t>
+          <t>Credential-free test gateway: a local sandbox page simulates success/failure/cancel through the real paid/receipt path.</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -4299,9 +4299,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K58" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>N: config + settings exist; full offline flow not confirmed.</t>
+          <t>L: TestGatewayAdapter + PaymentSandboxController + admin diagnostics; P: TestGateway + sandbox view + controller; T: Eskoofy_Test_Gateway + front-dashboard sandbox page; N: planTestGateway + /payments/sandbox. Unit-tested, no network.</t>
         </is>
       </c>
     </row>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Recurring fees / auto-invoice scheduler</t>
+          <t>Payment gateways — BD extended set (ShurjoPay/PortWallet/Cellfin/Purse/Cashby/UPay/MyCash/Payer)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Automatic recurring payment + invoice generation.</t>
+          <t>Config-driven hosted BD aggregators, seeded inactive until an admin supplies credentials.</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -4339,9 +4339,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -4349,34 +4349,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>L: RecurringPaymentService in scheduler; P: public/cron.php daily 01:00; T/N: no cron equivalent.</t>
+          <t>L/P: GenericHosted adapter rows in seeder; T: Generic Hosted Gateway registration; N: prisma/gateways.ts seed. Sandbox URLs are DRAFT pending vendor verification; no live calls in tests.</t>
         </is>
       </c>
     </row>
@@ -4386,17 +4386,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Leaves + leave types</t>
+          <t>Offline / bank-transfer payments</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Leave types, requests, approval workflow.</t>
+          <t>Manual offline payment approvals.</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -4429,9 +4429,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>T: leave-types.php / leave-requests.php; N: engine CRUD.</t>
+          <t>N: config + settings exist; full offline flow not confirmed.</t>
         </is>
       </c>
     </row>
@@ -4451,17 +4451,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Payroll: salary structures + payslips</t>
+          <t>Recurring fees / auto-invoice scheduler</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Define salary structures, generate + mark payslips paid.</t>
+          <t>Automatic recurring payment + invoice generation.</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -4484,29 +4484,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K61" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="L61" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>N: 'generic CRUD + generate screen' (NOT-IMPLEMENTED §4).</t>
+          <t>L: RecurringPaymentService in scheduler; P: public/cron.php daily 01:00; T/N: no cron equivalent.</t>
         </is>
       </c>
     </row>
@@ -4521,12 +4521,12 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Staff attendance (HR view)</t>
+          <t>Leaves + leave types</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>HR staff-attendance marking (shared screen, see Academics).</t>
+          <t>Leave types, requests, approval workflow.</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>T: staff-attendance.php; N: daily sheet.</t>
+          <t>T: leave-types.php / leave-requests.php; N: engine CRUD.</t>
         </is>
       </c>
     </row>
@@ -4581,17 +4581,17 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Admit cards</t>
+          <t>Payroll: salary structures + payslips</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Printable (L: PDF) admit cards per exam.</t>
+          <t>Define salary structures, generate + mark payslips paid.</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -4604,31 +4604,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G63" s="9" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="J63" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="K63" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>L: dompdf PDF. P: print Blade only, no composer runtime/dompdf. T: print page. N: print view, no PDF file (NOT-IMPLEMENTED §3).</t>
+          <t>N: 'generic CRUD + generate screen' (NOT-IMPLEMENTED §4).</t>
         </is>
       </c>
     </row>
@@ -4646,17 +4646,17 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Student ID cards</t>
+          <t>Staff attendance (HR view)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Printable (L: PDF) ID cards.</t>
+          <t>HR staff-attendance marking (shared screen, see Academics).</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -4669,29 +4669,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="H64" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="J64" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="K64" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>Same PDF story as admit cards.</t>
+          <t>T: staff-attendance.php; N: daily sheet.</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Certificates</t>
+          <t>Admit cards</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Printable (L: PDF) certificates.</t>
+          <t>Printable (L: PDF) admit cards per exam.</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>T: certificates.php; same PDF story.</t>
+          <t>L: dompdf PDF. P: print Blade only, no composer runtime/dompdf. T: print page. N: print view, no PDF file (NOT-IMPLEMENTED §3).</t>
         </is>
       </c>
     </row>
@@ -4781,12 +4781,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Testimonials (admin + public)</t>
+          <t>Student ID cards</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Testimonial records, front-page display.</t>
+          <t>Printable (L: PDF) ID cards.</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -4799,29 +4799,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>T: testimonials-admin.php.</t>
+          <t>Same PDF story as admit cards.</t>
         </is>
       </c>
     </row>
@@ -4846,12 +4846,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Committee members</t>
+          <t>Certificates</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Committee roster (admin + public page).</t>
+          <t>Printable (L: PDF) certificates.</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -4864,29 +4864,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>T: committee.php.</t>
+          <t>T: certificates.php; same PDF story.</t>
         </is>
       </c>
     </row>
@@ -4911,12 +4911,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Media library (upload + picker)</t>
+          <t>Testimonials (admin + public)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Upload files, browse, embed via media picker.</t>
+          <t>Testimonial records, front-page display.</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>N: media library upload + ?select=1 picker bespoke (NOT-IMPLEMENTED §2). P: MediaController.</t>
+          <t>T: testimonials-admin.php.</t>
         </is>
       </c>
     </row>
@@ -4971,17 +4971,17 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Library</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Books + book categories</t>
+          <t>Committee members</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Catalog + categories.</t>
+          <t>Committee roster (admin + public page).</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>T: library.php; N: engine CRUD.</t>
+          <t>T: committee.php.</t>
         </is>
       </c>
     </row>
@@ -5036,17 +5036,17 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Library</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Book issues (issue/return/fines)</t>
+          <t>Media library (upload + picker)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Issue/return tracking with overdue/fine handling.</t>
+          <t>Upload files, browse, embed via media picker.</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -5074,9 +5074,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J70" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>N: engine CRUD over book_issues.</t>
+          <t>N: media library upload + ?select=1 picker bespoke (NOT-IMPLEMENTED §2). P: MediaController.</t>
         </is>
       </c>
     </row>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Library reports</t>
+          <t>Books + book categories</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Issued/overdue/history reports.</t>
+          <t>Catalog + categories.</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>T: library-reports.php.</t>
+          <t>T: library.php; N: engine CRUD.</t>
         </is>
       </c>
     </row>
@@ -5166,17 +5166,17 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Library</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Events + calendar</t>
+          <t>Book issues (issue/return/fines)</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Events with calendar view.</t>
+          <t>Issue/return tracking with overdue/fine handling.</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -5204,9 +5204,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J72" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J72" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>T: events.php / events-calendar.php.</t>
+          <t>N: engine CRUD over book_issues.</t>
         </is>
       </c>
     </row>
@@ -5231,17 +5231,17 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Library</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Transport (vehicles/routes/assignments)</t>
+          <t>Library reports</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Vehicles, routes with stops, student assignments.</t>
+          <t>Issued/overdue/history reports.</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>N: wrong-table resolutions fixed → vehicles (NOT-IMPLEMENTED known-good).</t>
+          <t>T: library-reports.php.</t>
         </is>
       </c>
     </row>
@@ -5301,12 +5301,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Hostel (rooms/assignments)</t>
+          <t>Events + calendar</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Hostels, rooms, occupant assignments.</t>
+          <t>Events with calendar view.</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>T: hostels.php.</t>
+          <t>T: events.php / events-calendar.php.</t>
         </is>
       </c>
     </row>
@@ -5361,17 +5361,17 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Messages (internal)</t>
+          <t>Transport (vehicles/routes/assignments)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Internal messaging between users.</t>
+          <t>Vehicles, routes with stops, student assignments.</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>T: messages.php.</t>
+          <t>N: wrong-table resolutions fixed → vehicles (NOT-IMPLEMENTED known-good).</t>
         </is>
       </c>
     </row>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Bulk SMS campaign (compose/preview/send)</t>
+          <t>Hostel (rooms/assignments)</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>SMS campaign lifecycle.</t>
+          <t>Hostels, rooms, occupant assignments.</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -5444,9 +5444,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -5454,9 +5454,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
@@ -5464,14 +5464,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J76" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="K76" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>N: campaign lifecycle ported but no carrier delivery (NOT-IMPLEMENTED §4/§5).</t>
+          <t>T: hostels.php.</t>
         </is>
       </c>
     </row>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>SMS carrier delivery (Twilio/Vonage/TextLocal…)</t>
+          <t>Messages (internal)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Actual SMS send via a provider.</t>
+          <t>Internal messaging between users.</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -5509,9 +5509,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -5519,9 +5519,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
@@ -5529,24 +5529,24 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J77" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="K77" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L77" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>L: SMS_DRIVER drivers; P: config/sms.php 6 drivers; T: sms-gateway.php; N: not wired.</t>
+          <t>T: messages.php.</t>
         </is>
       </c>
     </row>
@@ -5561,12 +5561,12 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Notification templates</t>
+          <t>Bulk SMS campaign (compose/preview/send)</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Reusable notification content templates.</t>
+          <t>SMS campaign lifecycle.</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -5574,9 +5574,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -5584,9 +5584,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
@@ -5594,14 +5594,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K78" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J78" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>T: notification-templates.php.</t>
+          <t>N: campaign lifecycle ported but no carrier delivery (NOT-IMPLEMENTED §4/§5).</t>
         </is>
       </c>
     </row>
@@ -5626,12 +5626,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Notification preferences</t>
+          <t>SMS carrier delivery (Twilio/Vonage/TextLocal…)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Per-user notification preference toggles.</t>
+          <t>Actual SMS send via a provider.</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -5639,9 +5639,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -5649,9 +5649,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
@@ -5659,24 +5659,24 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K79" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J79" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>T: notification-preferences.php.</t>
+          <t>L: SMS_DRIVER drivers; P: config/sms.php 6 drivers; T: sms-gateway.php; N: not wired.</t>
         </is>
       </c>
     </row>
@@ -5691,12 +5691,12 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>In-app notifications inbox</t>
+          <t>Notification templates</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Notification stream with read/unread.</t>
+          <t>Reusable notification content templates.</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>N: bespoke inbox (NOT-IMPLEMENTED §2); T: notifications.php + REST notifications.</t>
+          <t>T: notification-templates.php.</t>
         </is>
       </c>
     </row>
@@ -5751,17 +5751,17 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Website CMS</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>CMS pages + content editing</t>
+          <t>Notification preferences</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Page content management with CMS editor.</t>
+          <t>Per-user notification preference toggles.</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -5794,9 +5794,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K81" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>N: CmsEdit typed editors done; live preview iframe + openMediaBrowser() missing (NOT-IMPLEMENTED §2).</t>
+          <t>T: notification-preferences.php.</t>
         </is>
       </c>
     </row>
@@ -5816,17 +5816,17 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Website CMS</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>CMS settings tab</t>
+          <t>In-app notifications inbox</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Website settings editor tab.</t>
+          <t>Notification stream with read/unread.</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -5849,29 +5849,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J82" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K82" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L82" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>T: 'CMS Settings absent in theme sidebar' (parity §1). N: 'about/cms/global-labels tabs remain' (NOT-IMPLEMENTED §2).</t>
+          <t>N: bespoke inbox (NOT-IMPLEMENTED §2); T: notifications.php + REST notifications.</t>
         </is>
       </c>
     </row>
@@ -5886,12 +5886,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Global labels</t>
+          <t>CMS pages + content editing</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>UI label overrides.</t>
+          <t>Page content management with CMS editor.</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -5914,29 +5914,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J83" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L83" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K83" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>T: 'Global Labels absent in theme sidebar' (parity §1). N: global-labels tab remains.</t>
+          <t>N: CmsEdit typed editors done; live preview iframe + openMediaBrowser() missing (NOT-IMPLEMENTED §2).</t>
         </is>
       </c>
     </row>
@@ -5951,12 +5951,12 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>News + article detail</t>
+          <t>CMS settings tab</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>News CRUD + public article pages.</t>
+          <t>Website settings editor tab.</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -5979,29 +5979,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J84" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K84" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L84" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L84" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>T: news.php + single-esk_news.php; N: /news + /news/{slug}.</t>
+          <t>T: 'CMS Settings absent in theme sidebar' (parity §1). N: 'about/cms/global-labels tabs remain' (NOT-IMPLEMENTED §2).</t>
         </is>
       </c>
     </row>
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Events (public + admin)</t>
+          <t>Global labels</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Events CRUD + public events listing.</t>
+          <t>UI label overrides.</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -6044,29 +6044,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J85" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K85" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L85" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>T: events.php + archive-esk_events.php.</t>
+          <t>T: 'Global Labels absent in theme sidebar' (parity §1). N: global-labels tab remains.</t>
         </is>
       </c>
     </row>
@@ -6081,12 +6081,12 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Gallery + lightbox</t>
+          <t>News + article detail</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Gallery CRUD + public gallery with lightbox.</t>
+          <t>News CRUD + public article pages.</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>T: gallery.php + archive-esk_galleries.php.</t>
+          <t>T: news.php + single-esk_news.php; N: /news + /news/{slug}.</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Announcements</t>
+          <t>Events (public + admin)</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Announcement posts.</t>
+          <t>Events CRUD + public events listing.</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>T: announcements.php.</t>
+          <t>T: events.php + archive-esk_events.php.</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Notices</t>
+          <t>Gallery + lightbox</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Notice board posts (admin + public, paginated).</t>
+          <t>Gallery CRUD + public gallery with lightbox.</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="M88" s="4" t="inlineStr">
         <is>
-          <t>T: notices.php + archive-esk_notices.php.</t>
+          <t>T: gallery.php + archive-esk_galleries.php.</t>
         </is>
       </c>
     </row>
@@ -6276,12 +6276,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Documents (website module)</t>
+          <t>Announcements</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>CMS-managed downloadable documents.</t>
+          <t>Announcement posts.</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>T: documents.php.</t>
+          <t>T: announcements.php.</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Contact / form submissions</t>
+          <t>Notices</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Contact form + submission inbox + export.</t>
+          <t>Notice board posts (admin + public, paginated).</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>T: contact-submissions.php.</t>
+          <t>T: notices.php + archive-esk_notices.php.</t>
         </is>
       </c>
     </row>
@@ -6406,12 +6406,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Careers + job applications</t>
+          <t>Documents (website module)</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Job postings + application tracking.</t>
+          <t>CMS-managed downloadable documents.</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>T: careers.php / career-applications.php + archive-esk_careers.php.</t>
+          <t>T: documents.php.</t>
         </is>
       </c>
     </row>
@@ -6466,17 +6466,17 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Public website</t>
+          <t>Website CMS</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Home page (hero/slider/CMS)</t>
+          <t>Contact / form submissions</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>CMS-driven homepage.</t>
+          <t>Contact form + submission inbox + export.</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>N: home real page (PORTING-STATUS).</t>
+          <t>T: contact-submissions.php.</t>
         </is>
       </c>
     </row>
@@ -6531,17 +6531,17 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Public website</t>
+          <t>Website CMS</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>About / academics / students / faculty / transport / committee pages</t>
+          <t>Careers + job applications</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Static + CMS info pages.</t>
+          <t>Job postings + application tracking.</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>T: template-*.php; N: real pages.</t>
+          <t>T: careers.php / career-applications.php + archive-esk_careers.php.</t>
         </is>
       </c>
     </row>
@@ -6601,12 +6601,12 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>News / notices / events / gallery listing pages</t>
+          <t>Home page (hero/slider/CMS)</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Public listings with detail pages.</t>
+          <t>CMS-driven homepage.</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="M94" s="4" t="inlineStr">
         <is>
-          <t>N: 28 public pages wired to app tables (PORTING-STATUS).</t>
+          <t>N: home real page (PORTING-STATUS).</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Public results lookup</t>
+          <t>About / academics / students / faculty / transport / committee pages</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>/results lookup by roll/batch.</t>
+          <t>Static + CMS info pages.</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>T: results lookup shortcode (README); N: /results real query.</t>
+          <t>T: template-*.php; N: real pages.</t>
         </is>
       </c>
     </row>
@@ -6731,12 +6731,12 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Routine page</t>
+          <t>News / notices / events / gallery listing pages</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Public timetable page.</t>
+          <t>Public listings with detail pages.</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="M96" s="4" t="inlineStr">
         <is>
-          <t>T: template via routines; N: /routine.</t>
+          <t>N: 28 public pages wired to app tables (PORTING-STATUS).</t>
         </is>
       </c>
     </row>
@@ -6796,12 +6796,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Contact page + form</t>
+          <t>Public results lookup</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Contact form + submissions (see CMS row).</t>
+          <t>/results lookup by roll/batch.</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -6844,7 +6844,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="M97" s="4" t="inlineStr"/>
+      <c r="M97" s="4" t="inlineStr">
+        <is>
+          <t>T: results lookup shortcode (README); N: /results real query.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -6857,12 +6861,12 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Site-wide search</t>
+          <t>Routine page</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Search public content.</t>
+          <t>Public timetable page.</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -6907,7 +6911,7 @@
       </c>
       <c r="M98" s="4" t="inlineStr">
         <is>
-          <t>T: search.php + template-search.php.</t>
+          <t>T: template via routines; N: /routine.</t>
         </is>
       </c>
     </row>
@@ -6922,12 +6926,12 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Payments page + status/receipts (public)</t>
+          <t>Contact page + form</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Public fee/invoice payment page.</t>
+          <t>Contact form + submissions (see CMS row).</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -6970,11 +6974,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="M99" s="4" t="inlineStr">
-        <is>
-          <t>T: fee payment shortcode; N: payments family pages.</t>
-        </is>
-      </c>
+      <c r="M99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Student/guardian portal</t>
+          <t>Site-wide search</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>/portal with admission + progress views.</t>
+          <t>Search public content.</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -7025,9 +7025,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K100" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="M100" s="4" t="inlineStr">
         <is>
-          <t>N: auth-gated portal; 'staff-role redirect + per-object 403 use simplified role match' (NOT-IMPLEMENTED §6).</t>
+          <t>T: search.php + template-search.php.</t>
         </is>
       </c>
     </row>
@@ -7052,12 +7052,12 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>sitemap.xml / robots.txt</t>
+          <t>Payments page + status/receipts (public)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>SEO outputs.</t>
+          <t>Public fee/invoice payment page.</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>N: sitemap.xml route present.</t>
+          <t>T: fee payment shortcode; N: payments family pages.</t>
         </is>
       </c>
     </row>
@@ -7112,17 +7112,17 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Public website</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>JSON API {success,message,data,meta} envelope</t>
+          <t>Student/guardian portal</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Standardized API response envelope.</t>
+          <t>/portal with admission + progress views.</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -7150,14 +7150,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J102" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="K102" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K102" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>L: StandardizeApiResponse; N: lib/api-response.ts (parity contract).</t>
+          <t>N: auth-gated portal; 'staff-role redirect + per-object 403 use simplified role match' (NOT-IMPLEMENTED §6).</t>
         </is>
       </c>
     </row>
@@ -7177,17 +7177,17 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Public website</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Results lookup API endpoint</t>
+          <t>sitemap.xml / robots.txt</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>GET /api/v1/academics/results/lookup.</t>
+          <t>SEO outputs.</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -7215,9 +7215,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J103" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>N: verified e2e (PORTING-STATUS).</t>
+          <t>N: sitemap.xml route present.</t>
         </is>
       </c>
     </row>
@@ -7247,12 +7247,12 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Generic REST over tables</t>
+          <t>JSON API {success,message,data,meta} envelope</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>CRUD JSON endpoints for records.</t>
+          <t>Standardized API response envelope.</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -7265,9 +7265,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G104" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
@@ -7275,9 +7275,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>L: typed api groups; P: 11 typed API controllers (README) — not fully generic; T: esk/v1 subset; N: generic engine over every table.</t>
+          <t>L: StandardizeApiResponse; N: lib/api-response.ts (parity contract).</t>
         </is>
       </c>
     </row>
@@ -7312,12 +7312,12 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Gateway webhooks / callbacks</t>
+          <t>Results lookup API endpoint</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>*/webhook/* + */callback/* endpoints.</t>
+          <t>GET /api/v1/academics/results/lookup.</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -7325,44 +7325,44 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F105" s="8" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J105" s="8" t="inlineStr">
         <is>
           <t>Not tested</t>
         </is>
       </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H105" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I105" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="J105" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="K105" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L105" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>L/P: gateway webhook surfaces; T: partial; N: not ported (NOT-IMPLEMENTED §5).</t>
+          <t>N: verified e2e (PORTING-STATUS).</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Notifications API</t>
+          <t>Generic REST over tables</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>List/mark-read notification endpoints.</t>
+          <t>CRUD JSON endpoints for records.</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -7395,9 +7395,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
@@ -7405,9 +7405,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>T: notifications in esk/v1 REST (README).</t>
+          <t>L: typed api groups; P: 11 typed API controllers (README) — not fully generic; T: esk/v1 subset; N: generic engine over every table.</t>
         </is>
       </c>
     </row>
@@ -7437,17 +7437,17 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>i18n (en + bn) string coverage</t>
+          <t>Gateway webhooks / callbacks</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>UI strings in both languages.</t>
+          <t>*/webhook/* + */callback/* endpoints.</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -7455,9 +7455,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -7465,34 +7465,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I107" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K107" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J107" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L107" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>L/P: lang/{en,bn}; T: .pot + bn_BD/en_GB .po; N: 742 keys x2 (parity-gated).</t>
+          <t>L/P: gateway webhook surfaces; T: partial; N: not ported (NOT-IMPLEMENTED §5).</t>
         </is>
       </c>
     </row>
@@ -7502,17 +7502,17 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Public-site locale switching</t>
+          <t>Notifications API</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Per-request ?lang / session locale switch.</t>
+          <t>List/mark-read notification endpoints.</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -7535,9 +7535,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I108" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
@@ -7545,9 +7545,9 @@
           <t>Not tested</t>
         </is>
       </c>
-      <c r="K108" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L108" s="6" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>L/P: /locale/{locale}; T: build-time .po profiles; N: public ?lang partially wired (NOT-IMPLEMENTED §8).</t>
+          <t>T: notifications in esk/v1 REST (README).</t>
         </is>
       </c>
     </row>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>PWA (manifest + service worker + offline)</t>
+          <t>i18n (en + bn) string coverage</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Installable/offline app shell.</t>
+          <t>UI strings in both languages.</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -7610,9 +7610,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K109" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="M109" s="4" t="inlineStr">
         <is>
-          <t>L: site.manifest route + sw.js + icons; P: /manifest.json route + sw.js + icons; T: pwa/ folder served; N: sw.js/offline/icons in public but not wired into layout.</t>
+          <t>L/P: lang/{en,bn}; T: .pot + bn_BD/en_GB .po; N: 742 keys x2 (parity-gated).</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>PDF file generation</t>
+          <t>Public-site locale switching</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Downloadable PDF (dompdf-equivalent).</t>
+          <t>Per-request ?lang / session locale switch.</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -7655,39 +7655,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G110" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H110" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I110" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K110" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L110" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="K110" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M110" s="4" t="inlineStr">
         <is>
-          <t>L: barryvdh/laravel-dompdf. P: no composer runtime → print views only. T: no PDF lib. N: printable HTML only.</t>
+          <t>L/P: /locale/{locale}; T: build-time .po profiles; N: public ?lang partially wired (NOT-IMPLEMENTED §8).</t>
         </is>
       </c>
     </row>
@@ -7702,12 +7702,12 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Scheduled jobs / cron</t>
+          <t>PWA (manifest + service worker + offline)</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Recurring payments, scheduled notifications, backups.</t>
+          <t>Installable/offline app shell.</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -7730,29 +7730,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I111" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J111" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K111" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L111" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K111" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>L: artisan scheduler (backup 02:00, queue monitor). P: public/cron.php (recurring + notifications). T/N: none.</t>
+          <t>L: site.manifest route + sw.js + icons; P: /manifest.json route + sw.js + icons; T: pwa/ folder served; N: sw.js/offline/icons in public but not wired into layout.</t>
         </is>
       </c>
     </row>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Queue worker / async jobs</t>
+          <t>PDF file generation</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Async job processing.</t>
+          <t>Downloadable PDF (dompdf-equivalent).</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>L: database/redis queue; P/T/N: no queue runtime.</t>
+          <t>L: barryvdh/laravel-dompdf. P: no composer runtime → print views only. T: no PDF lib. N: printable HTML only.</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Backups (manual + scheduled download)</t>
+          <t>Scheduled jobs / cron</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Database backup + download.</t>
+          <t>Recurring payments, scheduled notifications, backups.</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -7860,29 +7860,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I113" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J113" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K113" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="L113" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="I113" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J113" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L113" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>N: 'manual action only' per NOT-IMPLEMENTED §4; T: backup.php; P: BackupController.</t>
+          <t>L: artisan scheduler (backup 02:00, queue monitor). P: public/cron.php (recurring + notifications). T/N: none.</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Cloud backup (automatic, multi-provider, retention)</t>
+          <t>Queue worker / async jobs</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Upload a portable backup to Google Drive/Dropbox/4shared/S3/local mirror on a schedule, with retention pruning.</t>
+          <t>Async job processing.</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -7915,39 +7915,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J114" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K114" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L114" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I114" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J114" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K114" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L114" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>L: backup:cloud + 5-min dispatcher; P: scripts/backup-cloud.php + cron; T: inc/cloud-backup.php + WP-cron; N: lib/cloud-backup.ts + dispatch. See docs/design/CLOUD-BACKUP.md.</t>
+          <t>L: database/redis queue; P/T/N: no queue runtime.</t>
         </is>
       </c>
     </row>
@@ -7957,17 +7957,17 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Cross-cutting</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Configurable document designs &amp; watermarks</t>
+          <t>Backups (manual + scheduled download)</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Per-type themes (colours/fonts/borders/templates) + optional watermark for certificates, testimonials, marksheets, admit cards, ID cards.</t>
+          <t>Database backup + download.</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -8000,9 +8000,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K115" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K115" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>L: DocumentDesignService + document-designs admin; P: same service (byte-identical views); T: inc/document-designs.php; N: lib/document-designs.ts + dashboard page. See docs/design/DOCUMENT-DESIGNS.md.</t>
+          <t>N: 'manual action only' per NOT-IMPLEMENTED §4; T: backup.php; P: BackupController.</t>
         </is>
       </c>
     </row>
@@ -8027,12 +8027,12 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Activity log (audit trail)</t>
+          <t>Cloud backup (automatic, multi-provider, retention)</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Record user actions.</t>
+          <t>Upload a portable backup to Google Drive/Dropbox/4shared/S3/local mirror on a schedule, with retention pruning.</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>T: activity.php; N: 'activity log audit screen' bespoke (NOT-IMPLEMENTED §2).</t>
+          <t>L: backup:cloud + 5-min dispatcher; P: scripts/backup-cloud.php + cron; T: inc/cloud-backup.php + WP-cron; N: lib/cloud-backup.ts + dispatch. See docs/design/CLOUD-BACKUP.md.</t>
         </is>
       </c>
     </row>
@@ -8087,17 +8087,17 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Visitor logs</t>
+          <t>Configurable document designs &amp; watermarks</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Track visitor paths/locations.</t>
+          <t>Per-type themes (colours/fonts/borders/templates) + optional watermark for certificates, testimonials, marksheets, admit cards, ID cards.</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>T: visitor-logs.php; N: engine CRUD.</t>
+          <t>L: DocumentDesignService + document-designs admin; P: same service (byte-identical views); T: inc/document-designs.php; N: lib/document-designs.ts + dashboard page. See docs/design/DOCUMENT-DESIGNS.md.</t>
         </is>
       </c>
     </row>
@@ -8157,12 +8157,12 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Cache / tools admin</t>
+          <t>Activity log (audit trail)</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Clear caches + maintenance tools.</t>
+          <t>Record user actions.</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="M118" s="4" t="inlineStr">
         <is>
-          <t>T: cache.php / tools.php (theme tokens, parity §1); N: settings/tools surface.</t>
+          <t>T: activity.php; N: 'activity log audit screen' bespoke (NOT-IMPLEMENTED §2).</t>
         </is>
       </c>
     </row>
@@ -8222,12 +8222,12 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Mail settings + templates</t>
+          <t>Visitor logs</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>SMTP config + email templates.</t>
+          <t>Track visitor paths/locations.</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -8235,9 +8235,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F119" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -8245,24 +8245,24 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H119" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="J119" s="8" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="K119" s="9" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="M119" s="4" t="inlineStr">
         <is>
-          <t>N: mail_enabled + SMTP settings form, no queue/mailer (NOT-IMPLEMENTED §5).</t>
+          <t>T: visitor-logs.php; N: engine CRUD.</t>
         </is>
       </c>
     </row>
@@ -8287,55 +8287,185 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
+          <t>Cache / tools admin</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Clear caches + maintenance tools.</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L120" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M120" s="4" t="inlineStr">
+        <is>
+          <t>T: cache.php / tools.php (theme tokens, parity §1); N: settings/tools surface.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Mail settings + templates</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>SMTP config + email templates.</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J121" s="8" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="K121" s="9" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="L121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M121" s="4" t="inlineStr">
+        <is>
+          <t>N: mail_enabled + SMTP settings form, no queue/mailer (NOT-IMPLEMENTED §5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
           <t>Push notifications (FCM)</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D122" s="4" t="inlineStr">
         <is>
           <t>Firebase push delivery.</t>
         </is>
       </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F120" s="8" t="inlineStr">
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="inlineStr">
         <is>
           <t>Not tested</t>
         </is>
       </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H120" s="8" t="inlineStr">
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="inlineStr">
         <is>
           <t>Not tested</t>
         </is>
       </c>
-      <c r="I120" s="7" t="inlineStr">
+      <c r="I122" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J120" s="8" t="inlineStr">
+      <c r="J122" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K120" s="7" t="inlineStr">
+      <c r="K122" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L120" s="8" t="inlineStr">
+      <c r="L122" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M120" s="4" t="inlineStr">
+      <c r="M122" s="4" t="inlineStr">
         <is>
           <t>L/P: PUSH_DRIVER firebase in .env; T/N: not present.</t>
         </is>
@@ -8433,28 +8563,28 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>100</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>94.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>83.2</v>
+        <v>83.5</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
@@ -8479,13 +8609,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="7">
@@ -8513,10 +8643,10 @@
         <v>2.5</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="8">
@@ -8526,16 +8656,16 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>100</v>
@@ -8591,16 +8721,16 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13">
@@ -8610,16 +8740,16 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -8881,7 +9011,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
@@ -8916,7 +9046,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
@@ -8951,7 +9081,7 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
@@ -8986,7 +9116,7 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
@@ -9021,7 +9151,7 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
@@ -9056,7 +9186,7 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
@@ -9091,7 +9221,7 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
@@ -9126,7 +9256,7 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
@@ -9161,7 +9291,7 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
